--- a/data/2022/ESG_Download_Progress_2022.xlsx
+++ b/data/2022/ESG_Download_Progress_2022.xlsx
@@ -1546,7 +1546,7 @@
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
